--- a/research/traditional_assets/database/data/falkland_islands/falkland_islands_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/falkland_islands/falkland_islands_oil_gas_production_and_exploration.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.307</v>
+        <v>-0.261</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,31 +612,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.641</v>
+        <v>0.132</v>
       </c>
       <c r="V2">
-        <v>0.1614609571788413</v>
+        <v>0.04664310954063604</v>
       </c>
       <c r="W2">
-        <v>-0.0104778156996587</v>
+        <v>-0.008817567567567568</v>
       </c>
       <c r="X2">
-        <v>0.1460579283098052</v>
+        <v>0.1855061364942986</v>
       </c>
       <c r="Y2">
-        <v>-0.1565357440094639</v>
+        <v>-0.1943237040618661</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.01252609603340292</v>
+        <v>-0.008287578990987256</v>
       </c>
       <c r="AB2">
-        <v>0.1460579283098052</v>
+        <v>0.1855061364942986</v>
       </c>
       <c r="AC2">
-        <v>-0.1585840243432081</v>
+        <v>-0.1937937154852858</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.641</v>
+        <v>-0.132</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.192550315410033</v>
+        <v>-0.04892512972572276</v>
       </c>
       <c r="AK2">
-        <v>-0.0221347422217618</v>
+        <v>-0.004525507405375754</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.307</v>
+        <v>-0.261</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -710,31 +710,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.641</v>
+        <v>0.132</v>
       </c>
       <c r="V3">
-        <v>0.1614609571788413</v>
+        <v>0.04664310954063604</v>
       </c>
       <c r="W3">
-        <v>-0.0104778156996587</v>
+        <v>-0.008817567567567568</v>
       </c>
       <c r="X3">
-        <v>0.1460579283098052</v>
+        <v>0.1855061364942986</v>
       </c>
       <c r="Y3">
-        <v>-0.1565357440094639</v>
+        <v>-0.1943237040618661</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.01252609603340292</v>
+        <v>-0.008287578990987256</v>
       </c>
       <c r="AB3">
-        <v>0.1460579283098052</v>
+        <v>0.1855061364942986</v>
       </c>
       <c r="AC3">
-        <v>-0.1585840243432081</v>
+        <v>-0.1937937154852858</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.641</v>
+        <v>-0.132</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.192550315410033</v>
+        <v>-0.04892512972572276</v>
       </c>
       <c r="AK3">
-        <v>-0.0221347422217618</v>
+        <v>-0.004525507405375754</v>
       </c>
       <c r="AL3">
         <v>0</v>
